--- a/CLIENT/DATExx-Whiddon/2. Calculations/EOW/Grid Thresholds.xlsx
+++ b/CLIENT/DATExx-Whiddon/2. Calculations/EOW/Grid Thresholds.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://resrodel.sharepoint.com/sites/Customers/Shared Documents/IndoChinese Aged Care/4. Analysis/221219/2. Calculations/EOW/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\CentriNOTSYNC\ResidentialCare\CLIENT\DATExx-Whiddon\2. Calculations\EOW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="814" documentId="8_{C052F094-6189-4149-A0AB-972284330F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EED28BB-133F-4CF2-A256-A466C7512171}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AEF4C4-07B7-4F42-B3A0-F8D8905601C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1A6D2DB0-E7C1-4601-8836-610F057FFD94}"/>
   </bookViews>
@@ -38,6 +38,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -628,61 +629,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -901,6 +847,61 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1513,29 +1514,29 @@
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{47ECECC8-37DC-4B47-AC1B-0F51069BDAEA}" name="Point" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{096EA0A4-7FE5-4FEA-B771-A2821B46B18E}" name="Type" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B48FDB96-CF7A-491C-9995-297D75F914B6}" name="Threshold" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{84427775-C519-454A-A2B8-5D3E13FCEE09}" name="Date" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{1EA17C33-3054-4D8D-A96F-74411DD010F9}" name="Position" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{58435CA5-582A-47C5-B726-537F9E9032EB}" name="D" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{FBB23E2E-893E-4B69-8436-70D400E38CA2}" name="C" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{48CB5B79-4B74-4992-B41F-43ED9155B58A}" name="A" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{E1C205F7-1D30-4C7C-9240-E84EF6A5567C}" name="Ap" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{2FD6BD74-6D5A-4756-B4F4-89E89F6E60EC}" name="Ei" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{6A8AEA83-5BAF-45C4-B286-09F1DE237DA1}" name="Ii" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{C7F20865-BD25-4AA0-AECF-A86121DDF736}" name="Ai" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{567D81FF-87E5-4A2D-AA43-F8DC5C70E04C}" name="Ep" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{6E391C70-5677-4725-AAC3-78F7A001364E}" name="Ip" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{16CDBC69-049F-4993-90E2-0A667FDF132C}" name="X'" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{D817AAA6-D604-47EB-945F-8FE1383C51B6}" name="Y'" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{B48FDB96-CF7A-491C-9995-297D75F914B6}" name="Threshold" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{84427775-C519-454A-A2B8-5D3E13FCEE09}" name="Date" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{1EA17C33-3054-4D8D-A96F-74411DD010F9}" name="Position" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{58435CA5-582A-47C5-B726-537F9E9032EB}" name="D" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{FBB23E2E-893E-4B69-8436-70D400E38CA2}" name="C" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{48CB5B79-4B74-4992-B41F-43ED9155B58A}" name="A" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{E1C205F7-1D30-4C7C-9240-E84EF6A5567C}" name="Ap" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{2FD6BD74-6D5A-4756-B4F4-89E89F6E60EC}" name="Ei" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{6A8AEA83-5BAF-45C4-B286-09F1DE237DA1}" name="Ii" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{C7F20865-BD25-4AA0-AECF-A86121DDF736}" name="Ai" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{567D81FF-87E5-4A2D-AA43-F8DC5C70E04C}" name="Ep" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{6E391C70-5677-4725-AAC3-78F7A001364E}" name="Ip" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{16CDBC69-049F-4993-90E2-0A667FDF132C}" name="X'" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{D817AAA6-D604-47EB-945F-8FE1383C51B6}" name="Y'" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1573,7 +1574,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1679,7 +1680,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1821,7 +1822,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5053,12 +5054,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82d1b6b-c0e6-44b0-99a2-d357b2d50896">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3be0b85a-8471-4f10-b038-505fde09e598" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5263,28 +5266,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f82d1b6b-c0e6-44b0-99a2-d357b2d50896">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3be0b85a-8471-4f10-b038-505fde09e598" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D38CD96-7474-41CB-91EE-9DD5041D618A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CDBA317-EF8F-44DF-B124-1925E147E13C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f82d1b6b-c0e6-44b0-99a2-d357b2d50896"/>
+    <ds:schemaRef ds:uri="3be0b85a-8471-4f10-b038-505fde09e598"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DC51A4C-A427-44D2-BA54-54C1D656FE07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CDBA317-EF8F-44DF-B124-1925E147E13C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D38CD96-7474-41CB-91EE-9DD5041D618A}"/>
 </file>